--- a/doc/基本設計/03_API一覧.xlsx
+++ b/doc/基本設計/03_API一覧.xlsx
@@ -586,7 +586,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="27.62"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14.81"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="18.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="22.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="22.28"/>
   </cols>
   <sheetData>
     <row r="1" s="2" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
